--- a/artfynd/A 23494-2023 artfynd.xlsx
+++ b/artfynd/A 23494-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131036046</v>
       </c>
       <c r="B2" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>131242840</v>
       </c>
       <c r="B3" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 23494-2023 artfynd.xlsx
+++ b/artfynd/A 23494-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131036046</v>
       </c>
       <c r="B2" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>131242840</v>
       </c>
       <c r="B3" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 23494-2023 artfynd.xlsx
+++ b/artfynd/A 23494-2023 artfynd.xlsx
@@ -779,7 +779,7 @@
         <v>131242840</v>
       </c>
       <c r="B3" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 23494-2023 artfynd.xlsx
+++ b/artfynd/A 23494-2023 artfynd.xlsx
@@ -779,7 +779,7 @@
         <v>131242840</v>
       </c>
       <c r="B3" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 23494-2023 artfynd.xlsx
+++ b/artfynd/A 23494-2023 artfynd.xlsx
@@ -779,7 +779,7 @@
         <v>131242840</v>
       </c>
       <c r="B3" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 23494-2023 artfynd.xlsx
+++ b/artfynd/A 23494-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,14 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131036046</v>
+        <v>131035947</v>
       </c>
       <c r="B2" t="n">
-        <v>57884</v>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>327404</v>
+        <v>327287</v>
       </c>
       <c r="R2" t="n">
-        <v>6453512</v>
+        <v>6453517</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -764,26 +764,26 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Ann-Charlotte Svensson</t>
+          <t>Anna Svensson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ann-Charlotte Svensson</t>
+          <t>Anna Svensson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131242840</v>
+        <v>131036046</v>
       </c>
       <c r="B3" t="n">
-        <v>57899</v>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -807,22 +807,18 @@
       <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lille-Väktor, Boh</t>
+          <t>Sjöbacken, Boh</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>327428</v>
+        <v>327404</v>
       </c>
       <c r="R3" t="n">
-        <v>6453550</v>
+        <v>6453512</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -869,15 +865,230 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Anna Svensson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Anna Svensson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>131242840</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Lille-Väktor, Boh</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>327428</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6453550</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hjärtum</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>Liv Vikingson</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>Liv Vikingson</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>131035963</v>
+      </c>
+      <c r="B5" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Sjöbacken, Boh</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>327287</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6453517</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hjärtum</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Anna Svensson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Anna Svensson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 23494-2023 artfynd.xlsx
+++ b/artfynd/A 23494-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131035947</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131036046</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -979,6 +994,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131242840</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1089,8 +1109,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131035963</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>